--- a/results/consolidated/Stylized_Facts.xlsx
+++ b/results/consolidated/Stylized_Facts.xlsx
@@ -548,7 +548,7 @@
         <v>0.976912600799763</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0699007174643405</v>
+        <v>-0.0699007174643404</v>
       </c>
     </row>
     <row r="4">
